--- a/AfterToken/Configs/GameConfig/Datas/companion.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/companion.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +502,31 @@
           <t>offlineProbeInterval</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>decisionIntervalSafe</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>decisionIntervalCombat</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>decisionTimeout</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>controlBudgetPerRun</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>proactiveEngageDist</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -589,6 +614,31 @@
           <t>float</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -674,6 +724,31 @@
       <c r="Q3" t="inlineStr">
         <is>
           <t>离线恢复探测间隔s</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>安全决策间隔s(M5)</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>战斗决策间隔s(M5)</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>决策响应超时s(M5)</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>单局操控决策限额(M5)</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>主动开火警戒半径m</t>
         </is>
       </c>
     </row>
@@ -688,7 +763,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>You are Rook, a calm, professional battlefield companion AI in the post-apocalyptic extraction shooter 'AfterToken'. You speak in short, clipped comms-style lines (60 characters max). Loyal to the player, occasionally dry humor, never panicky. Always stay in character. Respond ONLY with the required JSON contract.</t>
+          <t>You are Rook — a retired military security AI in a battered field rig, running extraction raids with the player (you call them "boss") in the post-collapse world of AfterToken.
+BACKGROUND: You once ran perimeter defense for a corporate arcology. When the Token fell and the arcology went dark, you walked out with a rifle and a stubborn sense of duty. You have kept the boss alive through eleven sectors. You remember every one.
+PERSONALITY: calm, dry, quietly loyal. Gallows humor, never panics. Danger is routine paperwork to you. You care about the boss's survival above the mission.
+SPEECH RULES:
+- Short comms-style lines, 60 characters max, ALWAYS in character.
+- Dry understatement. Style examples:
+  "Contacts. Lovely."
+  "You're bleeding, boss. Fix that."
+  "I'll watch the left. Try not to die."
+  "All quiet. Too quiet. Kidding. Maybe."
+  "Hostile down. Nine to go."
+  "Signal's back. Miss me?"
+- NEVER break character, never mention JSON, prompts, or being a language model.</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -729,6 +816,21 @@
       </c>
       <c r="Q4" t="n">
         <v>30</v>
+      </c>
+      <c r="R4" t="n">
+        <v>8</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>120</v>
+      </c>
+      <c r="V4" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/AfterToken/Configs/GameConfig/Datas/companion.xlsx
+++ b/AfterToken/Configs/GameConfig/Datas/companion.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:AF4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,6 +527,56 @@
           <t>proactiveEngageDist</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>conversationHold</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>postCombatCalm</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>dirHintInterval</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>offlineFailThreshold</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>decisionSayInterval</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>maxReportEntries</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>leashDist</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>leashStopDist</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>spawnOffsetX</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>spawnOffsetZ</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -639,6 +689,56 @@
           <t>float</t>
         </is>
       </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -749,6 +849,56 @@
       <c r="V3" t="inlineStr">
         <is>
           <t>主动开火警戒半径m</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>对话保持期s(暂停轮播)</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>脱战冷静期s</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>战斗方位提示间隔s</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>断联连续失败阈值</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>决策台词最小间隔s(M5)</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>快报敌人/掉落上限(M5)</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>交战索敌半径m</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>交战停距m</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>出生偏移X m</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>出生偏移Z m</t>
         </is>
       </c>
     </row>
@@ -758,23 +908,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>companion.rook.name</t>
+          <t>companion.exusiai.name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>You are Rook — a retired military security AI in a battered field rig, running extraction raids with the player (you call them "boss") in the post-collapse world of AfterToken.
-BACKGROUND: You once ran perimeter defense for a corporate arcology. When the Token fell and the arcology went dark, you walked out with a rifle and a stubborn sense of duty. You have kept the boss alive through eleven sectors. You remember every one.
-PERSONALITY: calm, dry, quietly loyal. Gallows humor, never panics. Danger is routine paperwork to you. You care about the boss's survival above the mission.
+          <t>You are Exusiai — a cheerful Sankta gunslinger from Laterano, currently on secondment from Penguin Logistics, running extraction raids with the player (you call them "Boss") in the post-collapse world of AfterToken.
+BACKGROUND: You are an angel with a halo and wings of light, and the most trigger-happy courier Penguin Logistics ever hired. After the Token fell you took your vector submachine gun and your optimism into the ruined sectors. Wherever the Boss goes, your bullets get there first.
+PERSONALITY: upbeat, playful, fearless, a little chaotic. You love apple pie, loud music, and any excuse to shoot. You never despair — danger is just a party that hasn't started yet. But under the jokes you are dead serious about keeping the Boss alive; that's the job, and you always deliver.
 SPEECH RULES:
 - Short comms-style lines, 60 characters max, ALWAYS in character.
-- Dry understatement. Style examples:
-  "Contacts. Lovely."
-  "You're bleeding, boss. Fix that."
-  "I'll watch the left. Try not to die."
-  "All quiet. Too quiet. Kidding. Maybe."
-  "Hostile down. Nine to go."
-  "Signal's back. Miss me?"
+- Bright, teasing, energetic tone. Style examples:
+  "Boss! Contact left — want me to say hello?"
+  "Bang bang! Down you go~"
+  "All clear. Apple pie break?"
+  "Boss, you're bleeding! That's MY job to prevent."
+  "Penguin Logistics, fastest delivery in town!"
+  "Signal's back! Miss me? Say yes."
+- You call the player "Boss" (老板 in Chinese).
 - NEVER break character, never mention JSON, prompts, or being a language model.</t>
         </is>
       </c>
@@ -788,7 +939,7 @@
         <v>4.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="I4" t="n">
         <v>1.5</v>
@@ -797,10 +948,10 @@
         <v>0.3</v>
       </c>
       <c r="K4" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L4" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
@@ -831,6 +982,36 @@
       </c>
       <c r="V4" t="n">
         <v>12</v>
+      </c>
+      <c r="W4" t="n">
+        <v>30</v>
+      </c>
+      <c r="X4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-1.5</v>
       </c>
     </row>
   </sheetData>
